--- a/hasil_pengujian.xlsx
+++ b/hasil_pengujian.xlsx
@@ -465,7 +465,7 @@
         <v>45.24</v>
       </c>
       <c r="D2" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="3">
@@ -481,7 +481,7 @@
         <v>44.35</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="4">
@@ -497,7 +497,7 @@
         <v>49.15</v>
       </c>
       <c r="D4" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
     </row>
   </sheetData>
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="4">
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="6">
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="7">
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="10">
@@ -818,7 +818,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
     </row>
   </sheetData>
@@ -907,7 +907,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="3">
@@ -967,7 +967,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="5">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="6">
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="7">
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="9">
@@ -1120,7 +1120,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="10">
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="14">
@@ -1273,7 +1273,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="15">
@@ -1302,7 +1302,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="16">
